--- a/output/roomself_excel/1641.xlsx
+++ b/output/roomself_excel/1641.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29223</v>
+        <v>44964</v>
       </c>
       <c r="D2" t="n">
-        <v>1376</v>
+        <v>1792</v>
       </c>
       <c r="E2" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F2" t="n">
-        <v>214</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>272745</v>
+        <v>230672</v>
       </c>
       <c r="D3" t="n">
-        <v>6544</v>
+        <v>4388</v>
       </c>
       <c r="E3" t="n">
-        <v>874</v>
+        <v>781</v>
       </c>
       <c r="F3" t="n">
-        <v>407</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>230672</v>
+        <v>29223</v>
       </c>
       <c r="D4" t="n">
-        <v>4388</v>
+        <v>1376</v>
       </c>
       <c r="E4" t="n">
-        <v>781</v>
+        <v>243</v>
       </c>
       <c r="F4" t="n">
-        <v>483</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44964</v>
+        <v>272745</v>
       </c>
       <c r="D5" t="n">
-        <v>1792</v>
+        <v>6544</v>
       </c>
       <c r="E5" t="n">
-        <v>238</v>
+        <v>874</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         <v>3144</v>
       </c>
       <c r="E6" t="n">
-        <v>631</v>
+        <v>390</v>
       </c>
       <c r="F6" t="n">
-        <v>400</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">

--- a/output/roomself_excel/1641.xlsx
+++ b/output/roomself_excel/1641.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
         </is>
       </c>
     </row>
@@ -475,12 +555,32 @@
       <c r="D2" t="n">
         <v>1792</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>238</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>53</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +597,48 @@
       <c r="D3" t="n">
         <v>4388</v>
       </c>
-      <c r="E3" t="n">
-        <v>781</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>483</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>699</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>49</v>
+      </c>
+      <c r="M3" t="n">
+        <v>44</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +655,48 @@
       <c r="D4" t="n">
         <v>1376</v>
       </c>
-      <c r="E4" t="n">
-        <v>243</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>214</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>191</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>191</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +713,71 @@
       <c r="D5" t="n">
         <v>6544</v>
       </c>
-      <c r="E5" t="n">
-        <v>874</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>390</v>
+        <v>503</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>355</v>
+      </c>
+      <c r="J5" t="n">
+        <v>43</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>58</v>
+      </c>
+      <c r="M5" t="n">
+        <v>41</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>64</v>
+      </c>
+      <c r="P5" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>64</v>
+      </c>
+      <c r="S5" t="n">
+        <v>57</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>191</v>
+      </c>
+      <c r="V5" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +795,32 @@
       <c r="D6" t="n">
         <v>3144</v>
       </c>
-      <c r="E6" t="n">
-        <v>390</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>133</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="G6" t="n">
+        <v>43</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +837,40 @@
       <c r="D7" t="n">
         <v>1364</v>
       </c>
-      <c r="E7" t="n">
-        <v>225</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>202</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="G7" t="n">
+        <v>43</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>182</v>
+      </c>
+      <c r="J7" t="n">
+        <v>43</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/1641.xlsx
+++ b/output/roomself_excel/1641.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:AP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,106 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
         </is>
       </c>
     </row>
@@ -581,6 +681,38 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>112</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -639,6 +771,50 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>170</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>242</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -697,6 +873,38 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -777,6 +985,86 @@
         <v>191</v>
       </c>
       <c r="V5" t="n">
+        <v>41</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>111</v>
+      </c>
+      <c r="AP5" t="n">
         <v>41</v>
       </c>
     </row>
@@ -821,6 +1109,38 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -871,6 +1191,26 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
